--- a/data/trans_orig/Q46-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q46-Provincia-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su peso</t>
+          <t>Población según su peso (tasa de respuesta: 97,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>76,51; 79,6</t>
+          <t>76,37; 79,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>78,65; 81,79</t>
+          <t>78,69; 81,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77,74; 81,64</t>
+          <t>77,81; 81,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>80,38; 83,95</t>
+          <t>80,32; 83,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>62,69; 65,27</t>
+          <t>62,63; 65,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,78; 68,97</t>
+          <t>65,79; 69,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,84; 67,93</t>
+          <t>64,9; 67,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>66,31; 69,33</t>
+          <t>66,18; 69,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>69,87; 72,24</t>
+          <t>69,74; 72,26</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>72,67; 75,27</t>
+          <t>72,66; 75,1</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>71,67; 74,39</t>
+          <t>71,83; 74,6</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>74,01; 76,45</t>
+          <t>73,86; 76,46</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>75,5; 77,8</t>
+          <t>75,54; 77,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>76,61; 79,31</t>
+          <t>76,62; 79,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>76,67; 79,08</t>
+          <t>76,74; 79,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>79,26; 82,82</t>
+          <t>79,35; 82,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>64,91; 66,98</t>
+          <t>64,95; 67,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,02; 69,23</t>
+          <t>66,94; 69,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,06; 69,51</t>
+          <t>67,01; 69,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>66,98; 68,96</t>
+          <t>67,14; 68,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>70,35; 72,02</t>
+          <t>70,39; 71,99</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>72,03; 73,9</t>
+          <t>72,12; 74,15</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72,07; 73,94</t>
+          <t>72,06; 73,87</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>73,59; 75,73</t>
+          <t>73,61; 75,67</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>75,3; 77,54</t>
+          <t>75,28; 77,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>79,38; 82,17</t>
+          <t>79,34; 82,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>79,16; 81,96</t>
+          <t>79,17; 81,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>80,37; 83,72</t>
+          <t>80,53; 83,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>64,23; 66,6</t>
+          <t>64,25; 66,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>66,67; 69,72</t>
+          <t>66,82; 69,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>66,42; 69,45</t>
+          <t>66,58; 69,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>67,86; 70,41</t>
+          <t>67,94; 70,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>69,95; 71,82</t>
+          <t>69,91; 71,8</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>73,05; 75,33</t>
+          <t>73,17; 75,37</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>73,11; 75,3</t>
+          <t>72,98; 75,13</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>74,09; 76,43</t>
+          <t>74,25; 76,49</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>78,18; 80,34</t>
+          <t>78,14; 80,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>79,65; 82,49</t>
+          <t>79,77; 82,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78,65; 81,85</t>
+          <t>78,67; 81,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>79,24; 82,9</t>
+          <t>79,1; 82,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>64,56; 66,82</t>
+          <t>64,59; 66,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,95; 69,47</t>
+          <t>66,93; 69,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,31; 68,9</t>
+          <t>66,28; 68,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>63,32; 67,34</t>
+          <t>63,02; 67,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>71,43; 73,36</t>
+          <t>71,52; 73,33</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73,51; 75,72</t>
+          <t>73,58; 75,74</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72,61; 75,09</t>
+          <t>72,74; 75,12</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>68,27; 73,91</t>
+          <t>68,31; 73,85</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>76,12; 79,37</t>
+          <t>76,2; 79,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>78,87; 82,63</t>
+          <t>78,85; 82,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76,79; 80,35</t>
+          <t>76,83; 80,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>79,81; 82,82</t>
+          <t>79,79; 82,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>65,57; 69,43</t>
+          <t>65,54; 69,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,39; 67,83</t>
+          <t>64,27; 67,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>68,91; 71,79</t>
+          <t>69,04; 71,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>73,63; 575,82</t>
+          <t>72,94; 568,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>71,09; 74,1</t>
+          <t>71,35; 74,07</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71,84; 74,7</t>
+          <t>71,87; 74,84</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73,09; 75,51</t>
+          <t>73,15; 75,51</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>77,21; 439,37</t>
+          <t>77,27; 394,72</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>77,03; 79,66</t>
+          <t>77,09; 79,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>81,53; 85,11</t>
+          <t>81,32; 84,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>78,44; 81,71</t>
+          <t>78,5; 81,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>79,04; 82,0</t>
+          <t>79,06; 82,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>63,81; 66,36</t>
+          <t>63,77; 66,38</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>68,09; 71,29</t>
+          <t>68,04; 70,99</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>65,62; 68,56</t>
+          <t>65,71; 68,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>65,76; 68,37</t>
+          <t>65,8; 68,37</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>70,44; 72,67</t>
+          <t>70,55; 72,7</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>74,95; 77,74</t>
+          <t>74,88; 77,56</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>72,33; 74,85</t>
+          <t>72,09; 74,66</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>72,94; 75,14</t>
+          <t>72,84; 75,13</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>77,65; 79,43</t>
+          <t>77,73; 79,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>78,88; 80,81</t>
+          <t>79,02; 80,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>80,19; 82,42</t>
+          <t>80,31; 82,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>78,75; 81,61</t>
+          <t>78,68; 81,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>65,09; 67,12</t>
+          <t>65,1; 67,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,83; 69,84</t>
+          <t>67,83; 69,87</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,1; 67,31</t>
+          <t>65,3; 67,46</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>66,84; 77,34</t>
+          <t>66,84; 76,41</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>71,43; 72,95</t>
+          <t>71,44; 72,97</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>73,45; 75,01</t>
+          <t>73,42; 74,99</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>72,64; 74,44</t>
+          <t>72,62; 74,37</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>73,23; 77,62</t>
+          <t>73,13; 77,88</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>77,8; 79,57</t>
+          <t>77,74; 79,47</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>77,92; 79,64</t>
+          <t>77,9; 79,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>79,51; 81,51</t>
+          <t>79,36; 81,54</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78,35; 92,96</t>
+          <t>78,31; 93,29</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>64,15; 65,88</t>
+          <t>64,08; 65,84</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>66,41; 68,32</t>
+          <t>66,5; 68,29</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>67,57; 69,36</t>
+          <t>67,48; 69,37</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>67,63; 69,32</t>
+          <t>67,62; 69,23</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>70,92; 72,27</t>
+          <t>70,85; 72,33</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>72,12; 73,6</t>
+          <t>72,18; 73,6</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>73,48; 74,96</t>
+          <t>73,47; 74,97</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>73,16; 86,5</t>
+          <t>73,26; 85,98</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>77,56; 78,36</t>
+          <t>77,57; 78,36</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>79,45; 80,33</t>
+          <t>79,4; 80,34</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>79,51; 80,47</t>
+          <t>79,48; 80,41</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>80,32; 86,05</t>
+          <t>80,3; 86,48</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>65,1; 65,97</t>
+          <t>65,11; 65,94</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>67,55; 68,43</t>
+          <t>67,54; 68,46</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>67,23; 68,13</t>
+          <t>67,22; 68,11</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>68,34; 129,69</t>
+          <t>68,42; 149,16</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>71,33; 71,99</t>
+          <t>71,35; 71,98</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>73,52; 74,22</t>
+          <t>73,49; 74,21</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>73,33; 74,1</t>
+          <t>73,32; 74,07</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>74,57; 105,93</t>
+          <t>74,75; 107,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q46-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q46-Provincia-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>82,0</t>
+          <t>82,01</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>67,66</t>
+          <t>67,9</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>75,12</t>
+          <t>75,01</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>76,37; 79,56</t>
+          <t>76,48; 79,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>78,69; 81,68</t>
+          <t>78,59; 81,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77,81; 81,77</t>
+          <t>77,64; 81,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>80,32; 83,99</t>
+          <t>80,64; 83,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>62,63; 65,42</t>
+          <t>62,61; 65,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,79; 69,01</t>
+          <t>65,73; 69,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,9; 67,89</t>
+          <t>65,04; 68,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>66,18; 69,27</t>
+          <t>66,57; 69,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>69,74; 72,26</t>
+          <t>69,77; 72,15</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>72,66; 75,1</t>
+          <t>72,66; 75,21</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>71,83; 74,6</t>
+          <t>71,65; 74,64</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>73,86; 76,46</t>
+          <t>73,78; 76,15</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>81,07</t>
+          <t>81,17</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>67,99</t>
+          <t>67,91</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>74,61</t>
+          <t>74,5</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>75,54; 77,83</t>
+          <t>75,45; 77,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>76,62; 79,46</t>
+          <t>76,6; 79,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>76,74; 79,16</t>
+          <t>76,56; 78,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>79,35; 82,69</t>
+          <t>79,5; 82,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>64,95; 67,0</t>
+          <t>64,97; 67,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,94; 69,29</t>
+          <t>66,96; 69,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,01; 69,42</t>
+          <t>66,96; 69,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>67,14; 68,91</t>
+          <t>67,04; 68,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>70,39; 71,99</t>
+          <t>70,36; 72,05</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>72,12; 74,15</t>
+          <t>72,09; 73,92</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72,06; 73,87</t>
+          <t>72,06; 73,91</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>73,61; 75,67</t>
+          <t>73,48; 75,52</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>82,04</t>
+          <t>82,53</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>69,18</t>
+          <t>69,27</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>75,31</t>
+          <t>75,51</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>75,28; 77,55</t>
+          <t>75,31; 77,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>79,34; 82,09</t>
+          <t>79,43; 82,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>79,17; 81,91</t>
+          <t>79,24; 81,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>80,53; 83,83</t>
+          <t>81,06; 84,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>64,25; 66,74</t>
+          <t>64,24; 66,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>66,82; 69,71</t>
+          <t>66,83; 69,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>66,58; 69,55</t>
+          <t>66,58; 69,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>67,94; 70,44</t>
+          <t>68,04; 70,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>69,91; 71,8</t>
+          <t>69,85; 71,73</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>73,17; 75,37</t>
+          <t>73,06; 75,4</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>72,98; 75,13</t>
+          <t>73,1; 75,31</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>74,25; 76,49</t>
+          <t>74,4; 76,64</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80,93</t>
+          <t>80,6</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>65,72</t>
+          <t>66,96</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>72,03</t>
+          <t>73,37</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>78,14; 80,41</t>
+          <t>78,02; 80,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>79,77; 82,45</t>
+          <t>79,69; 82,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78,67; 81,9</t>
+          <t>78,44; 81,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>79,1; 82,95</t>
+          <t>78,9; 82,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>64,59; 66,9</t>
+          <t>64,61; 66,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,93; 69,64</t>
+          <t>67,0; 69,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,28; 68,99</t>
+          <t>66,28; 69,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>63,02; 67,36</t>
+          <t>65,68; 68,28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>71,52; 73,33</t>
+          <t>71,48; 73,34</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73,58; 75,74</t>
+          <t>73,54; 75,61</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72,74; 75,12</t>
+          <t>72,72; 74,98</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>68,31; 73,85</t>
+          <t>72,28; 74,71</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>81,31</t>
+          <t>80,9</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>251,37</t>
+          <t>77,84</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>181,8</t>
+          <t>79,29</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>76,2; 79,74</t>
+          <t>76,12; 79,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>78,85; 82,56</t>
+          <t>79,02; 82,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76,83; 80,36</t>
+          <t>76,86; 80,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>79,79; 82,88</t>
+          <t>79,54; 82,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>65,54; 69,64</t>
+          <t>65,62; 69,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,27; 67,65</t>
+          <t>64,32; 67,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,04; 71,88</t>
+          <t>68,9; 71,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>72,94; 568,85</t>
+          <t>72,26; 91,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>71,35; 74,07</t>
+          <t>71,23; 74,02</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71,87; 74,84</t>
+          <t>71,75; 74,76</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73,15; 75,51</t>
+          <t>73,02; 75,52</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>77,27; 394,72</t>
+          <t>76,16; 86,45</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>80,44</t>
+          <t>80,25</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>67,03</t>
+          <t>67,3</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>73,93</t>
+          <t>73,89</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>77,09; 79,68</t>
+          <t>77,0; 79,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>81,32; 84,89</t>
+          <t>81,45; 85,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>78,5; 81,97</t>
+          <t>78,48; 81,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>79,06; 82,13</t>
+          <t>79,0; 81,89</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>63,77; 66,38</t>
+          <t>63,78; 66,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>68,04; 70,99</t>
+          <t>67,91; 71,06</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>65,71; 68,65</t>
+          <t>65,42; 68,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>65,8; 68,37</t>
+          <t>66,07; 68,49</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>70,55; 72,7</t>
+          <t>70,47; 72,66</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>74,88; 77,56</t>
+          <t>74,85; 77,57</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>72,09; 74,66</t>
+          <t>72,29; 74,84</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>72,84; 75,13</t>
+          <t>72,94; 75,03</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>80,03</t>
+          <t>80,16</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>70,89</t>
+          <t>67,43</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>74,78</t>
+          <t>73,6</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>77,73; 79,48</t>
+          <t>77,57; 79,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>79,02; 80,91</t>
+          <t>79,0; 80,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>80,31; 82,45</t>
+          <t>80,34; 82,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>78,68; 81,4</t>
+          <t>78,82; 81,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>65,1; 67,16</t>
+          <t>65,03; 67,05</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,83; 69,87</t>
+          <t>67,73; 69,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,3; 67,46</t>
+          <t>65,15; 67,4</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>66,84; 76,41</t>
+          <t>66,45; 68,38</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>71,44; 72,97</t>
+          <t>71,41; 72,96</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>73,42; 74,99</t>
+          <t>73,5; 75,0</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>72,62; 74,37</t>
+          <t>72,62; 74,4</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>73,13; 77,88</t>
+          <t>72,69; 74,43</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>84,31</t>
+          <t>78,33</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>68,42</t>
+          <t>68,58</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>77,42</t>
+          <t>73,37</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>77,74; 79,47</t>
+          <t>77,83; 79,52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>77,9; 79,67</t>
+          <t>77,85; 79,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>79,36; 81,54</t>
+          <t>79,45; 81,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78,31; 93,29</t>
+          <t>77,44; 79,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>64,08; 65,84</t>
+          <t>64,08; 65,81</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>66,5; 68,29</t>
+          <t>66,46; 68,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>67,48; 69,37</t>
+          <t>67,4; 69,33</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>67,62; 69,23</t>
+          <t>67,82; 69,42</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>70,85; 72,33</t>
+          <t>70,89; 72,3</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>72,18; 73,6</t>
+          <t>72,25; 73,65</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>73,47; 74,97</t>
+          <t>73,52; 74,98</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>73,26; 85,98</t>
+          <t>72,66; 74,05</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>81,88</t>
+          <t>80,37</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>81,67</t>
+          <t>68,57</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>81,77</t>
+          <t>74,33</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>77,57; 78,36</t>
+          <t>77,55; 78,4</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>79,4; 80,34</t>
+          <t>79,43; 80,33</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>79,48; 80,41</t>
+          <t>79,44; 80,4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>80,3; 86,48</t>
+          <t>79,88; 80,91</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>65,11; 65,94</t>
+          <t>65,13; 65,98</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>67,54; 68,46</t>
+          <t>67,59; 68,47</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>67,22; 68,11</t>
+          <t>67,21; 68,11</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>68,42; 149,16</t>
+          <t>68,03; 69,44</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>71,35; 71,98</t>
+          <t>71,35; 72,0</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>73,49; 74,21</t>
+          <t>73,5; 74,19</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>73,32; 74,07</t>
+          <t>73,31; 74,06</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>74,75; 107,21</t>
+          <t>73,95; 74,9</t>
         </is>
       </c>
     </row>
